--- a/agriculture 53.xlsx
+++ b/agriculture 53.xlsx
@@ -223,13 +223,31 @@
     <t xml:space="preserve">2020-21</t>
   </si>
   <si>
+    <t xml:space="preserve">Unit:- </t>
+  </si>
+  <si>
     <t xml:space="preserve">Source:  EPWRF (Economic &amp; Political Weekly  Reasearch Foundation) 1964-2021</t>
   </si>
   <si>
-    <t xml:space="preserve">Source Description: </t>
-  </si>
-  <si>
-    <t xml:space="preserve">1966-67 to 2007-08: Plantation Crops: Arecanut:-&gt; Directorate of Economics and Statistics, Dept. of Agriculture, Cooperation and Farmers Welfare, Ministry of Agriculture, Govt. of India</t>
+    <r>
+      <rPr>
+        <b val="true"/>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Source Description: </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">1966-67 to 2007-08: Plantation Crops: Arecanut:-&gt; Directorate of Economics and Statistics, Dept. of Agriculture, Cooperation and Farmers Welfare, Ministry of Agriculture, Govt. of India</t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">2008-09 to 2015-16: Plantation Crops: Arecanut:-&gt; Indian Horticulture Database, National Horticulture Board</t>
@@ -247,7 +265,7 @@
     <numFmt numFmtId="165" formatCode="0.0"/>
     <numFmt numFmtId="166" formatCode="0.00"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -289,7 +307,13 @@
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <charset val="1"/>
+    </font>
+    <font>
+      <b val="true"/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -353,8 +377,8 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
@@ -393,7 +417,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -419,9 +443,9 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:M1048576"/>
-  <sheetFormatPr defaultColWidth="10.78515625" defaultRowHeight="14.4" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="10.796875" defaultRowHeight="14.4" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
-    <row r="1" customFormat="false" ht="28.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2410,54 +2434,99 @@
         <v>10.8108108108108</v>
       </c>
     </row>
-    <row r="56" customFormat="false" ht="25.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A56" s="10" t="s">
+    <row r="56" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A56" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="B56" s="10"/>
-      <c r="C56" s="10"/>
-      <c r="D56" s="10"/>
-    </row>
-    <row r="57" customFormat="false" ht="21.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A57" s="11" t="s">
+      <c r="B56" s="3"/>
+      <c r="C56" s="3"/>
+      <c r="D56" s="3"/>
+      <c r="E56" s="3"/>
+      <c r="F56" s="3"/>
+      <c r="G56" s="3"/>
+      <c r="H56" s="3"/>
+      <c r="I56" s="3"/>
+      <c r="J56" s="3"/>
+      <c r="K56" s="3"/>
+      <c r="L56" s="3"/>
+      <c r="M56" s="3"/>
+    </row>
+    <row r="57" customFormat="false" ht="25.2" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A57" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="B57" s="11"/>
-      <c r="C57" s="11"/>
-      <c r="D57" s="11"/>
-    </row>
-    <row r="58" customFormat="false" ht="31.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A58" s="12" t="s">
+      <c r="B57" s="10"/>
+      <c r="C57" s="10"/>
+      <c r="D57" s="10"/>
+      <c r="E57" s="10"/>
+      <c r="F57" s="10"/>
+      <c r="G57" s="10"/>
+      <c r="H57" s="10"/>
+      <c r="I57" s="10"/>
+      <c r="J57" s="10"/>
+      <c r="K57" s="10"/>
+      <c r="L57" s="10"/>
+      <c r="M57" s="10"/>
+    </row>
+    <row r="58" customFormat="false" ht="21.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A58" s="11" t="s">
         <v>69</v>
       </c>
-      <c r="B58" s="12"/>
-      <c r="C58" s="12"/>
-      <c r="D58" s="12"/>
-    </row>
-    <row r="59" customFormat="false" ht="50.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="B58" s="11"/>
+      <c r="C58" s="11"/>
+      <c r="D58" s="11"/>
+      <c r="E58" s="11"/>
+      <c r="F58" s="11"/>
+      <c r="G58" s="11"/>
+      <c r="H58" s="11"/>
+      <c r="I58" s="11"/>
+      <c r="J58" s="11"/>
+      <c r="K58" s="11"/>
+      <c r="L58" s="11"/>
+      <c r="M58" s="11"/>
+    </row>
+    <row r="59" customFormat="false" ht="31.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="12" t="s">
         <v>70</v>
       </c>
       <c r="B59" s="12"/>
       <c r="C59" s="12"/>
       <c r="D59" s="12"/>
-    </row>
-    <row r="60" customFormat="false" ht="47.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="E59" s="12"/>
+      <c r="F59" s="12"/>
+      <c r="G59" s="12"/>
+      <c r="H59" s="12"/>
+      <c r="I59" s="12"/>
+      <c r="J59" s="12"/>
+      <c r="K59" s="12"/>
+      <c r="L59" s="12"/>
+      <c r="M59" s="12"/>
+    </row>
+    <row r="60" customFormat="false" ht="50.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="12" t="s">
         <v>71</v>
       </c>
       <c r="B60" s="12"/>
       <c r="C60" s="12"/>
       <c r="D60" s="12"/>
+      <c r="E60" s="12"/>
+      <c r="F60" s="12"/>
+      <c r="G60" s="12"/>
+      <c r="H60" s="12"/>
+      <c r="I60" s="12"/>
+      <c r="J60" s="12"/>
+      <c r="K60" s="12"/>
+      <c r="L60" s="12"/>
+      <c r="M60" s="12"/>
     </row>
     <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <mergeCells count="5">
-    <mergeCell ref="A56:D56"/>
-    <mergeCell ref="A57:D57"/>
-    <mergeCell ref="A58:D58"/>
-    <mergeCell ref="A59:D59"/>
-    <mergeCell ref="A60:D60"/>
+    <mergeCell ref="A56:M56"/>
+    <mergeCell ref="A57:M57"/>
+    <mergeCell ref="A58:M58"/>
+    <mergeCell ref="A59:M59"/>
+    <mergeCell ref="A60:M60"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>

--- a/agriculture 53.xlsx
+++ b/agriculture 53.xlsx
@@ -223,7 +223,7 @@
     <t xml:space="preserve">2020-21</t>
   </si>
   <si>
-    <t xml:space="preserve">Unit:- </t>
+    <t xml:space="preserve">Unit:- Percentage(%)</t>
   </si>
   <si>
     <t xml:space="preserve">Source:  EPWRF (Economic &amp; Political Weekly  Reasearch Foundation) 1964-2021</t>
@@ -236,6 +236,7 @@
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Source Description: </t>
     </r>
@@ -245,6 +246,7 @@
         <color rgb="FF000000"/>
         <rFont val="Calibri"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">1966-67 to 2007-08: Plantation Crops: Arecanut:-&gt; Directorate of Economics and Statistics, Dept. of Agriculture, Cooperation and Farmers Welfare, Ministry of Agriculture, Govt. of India</t>
     </r>
@@ -265,7 +267,7 @@
     <numFmt numFmtId="165" formatCode="0.0"/>
     <numFmt numFmtId="166" formatCode="0.00"/>
   </numFmts>
-  <fonts count="8">
+  <fonts count="7">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -307,13 +309,7 @@
       <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -417,7 +413,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -443,7 +439,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:M1048576"/>
-  <sheetFormatPr defaultColWidth="10.796875" defaultRowHeight="14.4" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="10.8125" defaultRowHeight="14.4" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">

--- a/agriculture 53.xlsx
+++ b/agriculture 53.xlsx
@@ -223,7 +223,7 @@
     <t xml:space="preserve">2020-21</t>
   </si>
   <si>
-    <t xml:space="preserve">Unit:- Percentage(%)</t>
+    <t xml:space="preserve">Unit:- Percentage (%)</t>
   </si>
   <si>
     <t xml:space="preserve">Source:  EPWRF (Economic &amp; Political Weekly  Reasearch Foundation) 1964-2021</t>
@@ -439,7 +439,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:M1048576"/>
-  <sheetFormatPr defaultColWidth="10.8125" defaultRowHeight="14.4" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="10.82421875" defaultRowHeight="14.4" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="28.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
